--- a/JsonConverter/ExcelFiles/Planet.xlsx
+++ b/JsonConverter/ExcelFiles/Planet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="11520" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="98">
   <si>
     <t>아이디</t>
   </si>
@@ -102,64 +102,64 @@
     <t>Small</t>
   </si>
   <si>
-    <t>Vesta4</t>
-  </si>
-  <si>
-    <t>earth/earth_0</t>
+    <t>velora</t>
+  </si>
+  <si>
+    <t>Planet/Planet_0</t>
   </si>
   <si>
     <t>Planet_small_02</t>
   </si>
   <si>
-    <t>Echo</t>
-  </si>
-  <si>
-    <t>earth/earth_1</t>
+    <t>cindara</t>
+  </si>
+  <si>
+    <t>Planet/Planet_1</t>
   </si>
   <si>
     <t>Planet_small_03</t>
   </si>
   <si>
-    <t>Zion</t>
-  </si>
-  <si>
-    <t>earth/earth_2</t>
+    <t>virena</t>
+  </si>
+  <si>
+    <t>Planet/Planet_2</t>
   </si>
   <si>
     <t>Planet_small_04</t>
   </si>
   <si>
-    <t>Shurin</t>
-  </si>
-  <si>
-    <t>earth/earth_3</t>
+    <t>crysalis</t>
+  </si>
+  <si>
+    <t>Planet/Planet_3</t>
   </si>
   <si>
     <t>Planet_small_05</t>
   </si>
   <si>
-    <t>Platon</t>
-  </si>
-  <si>
-    <t>exoplanet1</t>
+    <t>dravos</t>
+  </si>
+  <si>
+    <t>Planet/Planet_4</t>
   </si>
   <si>
     <t>Planet_small_06</t>
   </si>
   <si>
-    <t>Kort</t>
-  </si>
-  <si>
-    <t>exoplanet2</t>
+    <t>seradon</t>
+  </si>
+  <si>
+    <t>Planet/Planet_5</t>
   </si>
   <si>
     <t>Planet_small_07</t>
   </si>
   <si>
-    <t>Pyros</t>
-  </si>
-  <si>
-    <t>exoplanet3</t>
+    <t>velora_minor</t>
+  </si>
+  <si>
+    <t>Planet/Planet_6</t>
   </si>
   <si>
     <t>Planet_medium_01</t>
@@ -168,46 +168,46 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>Terris</t>
-  </si>
-  <si>
-    <t>exoplanet4</t>
+    <t>joralis</t>
+  </si>
+  <si>
+    <t>Planet/Planet_7</t>
   </si>
   <si>
     <t>Planet_medium_02</t>
   </si>
   <si>
-    <t>Aurelia</t>
-  </si>
-  <si>
-    <t>exoplanet5</t>
+    <t>mekaron</t>
+  </si>
+  <si>
+    <t>Planet/Planet_8</t>
   </si>
   <si>
     <t>Planet_medium_03</t>
   </si>
   <si>
-    <t>KeplerB</t>
-  </si>
-  <si>
-    <t>exoplanet6</t>
+    <t>talmeris</t>
+  </si>
+  <si>
+    <t>Planet/Planet_9</t>
   </si>
   <si>
     <t>Planet_medium_04</t>
   </si>
   <si>
-    <t>Veridian</t>
-  </si>
-  <si>
-    <t>jupiter</t>
+    <t>pyrenox</t>
+  </si>
+  <si>
+    <t>Planet/Planet_10</t>
   </si>
   <si>
     <t>Planet_medium_05</t>
   </si>
   <si>
-    <t>Nova Prime</t>
-  </si>
-  <si>
-    <t>mars</t>
+    <t>nereth</t>
+  </si>
+  <si>
+    <t>Planet/Planet_11</t>
   </si>
   <si>
     <t>Planet_Large_01</t>
@@ -216,46 +216,46 @@
     <t>Large</t>
   </si>
   <si>
-    <t>Goliath</t>
-  </si>
-  <si>
-    <t>mercury</t>
+    <t>frosena</t>
+  </si>
+  <si>
+    <t>Planet/Planet_12</t>
   </si>
   <si>
     <t>Planet_Large_02</t>
   </si>
   <si>
-    <t>Titanos</t>
-  </si>
-  <si>
-    <t>moon1</t>
+    <t>peloris</t>
+  </si>
+  <si>
+    <t>Planet/Planet_13</t>
   </si>
   <si>
     <t>Planet_Large_03</t>
   </si>
   <si>
-    <t>Azureus</t>
-  </si>
-  <si>
-    <t>moon2</t>
+    <t>orbion</t>
+  </si>
+  <si>
+    <t>Planet/Planet_14</t>
   </si>
   <si>
     <t>Planet_Large_04</t>
   </si>
   <si>
-    <t>Thanos</t>
-  </si>
-  <si>
-    <t>neptune</t>
+    <t>castren</t>
+  </si>
+  <si>
+    <t>Planet/Planet_15</t>
   </si>
   <si>
     <t>Planet_Large_05</t>
   </si>
   <si>
-    <t>Osiris</t>
-  </si>
-  <si>
-    <t>pluto</t>
+    <t>umbraka</t>
+  </si>
+  <si>
+    <t>Planet/Planet_16</t>
   </si>
   <si>
     <t>Planet_Super_01</t>
@@ -264,43 +264,64 @@
     <t>Super</t>
   </si>
   <si>
-    <t>Aethelgard</t>
-  </si>
-  <si>
-    <t>saturn</t>
+    <t>lumiris</t>
+  </si>
+  <si>
+    <t>Planet/Planet_17</t>
   </si>
   <si>
     <t>Planet_Super_02</t>
   </si>
   <si>
-    <t>Behemoth</t>
-  </si>
-  <si>
-    <t>sun</t>
+    <t>mordaris</t>
+  </si>
+  <si>
+    <t>Planet/Planet_18</t>
   </si>
   <si>
     <t>Planet_Super_03</t>
   </si>
   <si>
-    <t>Chronos</t>
-  </si>
-  <si>
-    <t>uranus</t>
+    <t>rathen</t>
+  </si>
+  <si>
+    <t>Planet/Planet_19</t>
   </si>
   <si>
     <t>Planet_Super_04</t>
   </si>
   <si>
-    <t>Hyperion</t>
-  </si>
-  <si>
-    <t>venus</t>
+    <t>volkris</t>
+  </si>
+  <si>
+    <t>Planet/Planet_20</t>
   </si>
   <si>
     <t>Planet_Super_05</t>
   </si>
   <si>
-    <t>OmniX</t>
+    <t>eldara</t>
+  </si>
+  <si>
+    <t>Planet/Planet_21</t>
+  </si>
+  <si>
+    <t>Planet_Super_06</t>
+  </si>
+  <si>
+    <t>shardon</t>
+  </si>
+  <si>
+    <t>Planet/Planet_22</t>
+  </si>
+  <si>
+    <t>Planet_Super_07</t>
+  </si>
+  <si>
+    <t>nyxor</t>
+  </si>
+  <si>
+    <t>Planet/Planet_23</t>
   </si>
 </sst>
 </file>
@@ -313,13 +334,25 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -786,142 +819,148 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1448,7 +1487,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.2222222222222" customWidth="1"/>
@@ -1549,14 +1588,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" ht="15.6" spans="1:9">
       <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D4">
@@ -1579,14 +1618,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" ht="15.6" spans="1:9">
       <c r="A5" t="s">
         <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D5">
@@ -1609,14 +1648,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" ht="15.6" spans="1:9">
       <c r="A6" t="s">
         <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D6">
@@ -1639,14 +1678,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" ht="15.6" spans="1:9">
       <c r="A7" t="s">
         <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D7">
@@ -1669,14 +1708,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" ht="15.6" spans="1:9">
       <c r="A8" t="s">
         <v>35</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D8">
@@ -1693,20 +1732,20 @@
         <v>80</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" ht="15.6" spans="1:9">
       <c r="A9" t="s">
         <v>38</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D9">
@@ -1723,20 +1762,20 @@
         <v>80</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" ht="15.6" spans="1:9">
       <c r="A10" t="s">
         <v>41</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D10">
@@ -1753,20 +1792,20 @@
         <v>80</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" ht="15.6" spans="1:9">
       <c r="A11" t="s">
         <v>44</v>
       </c>
       <c r="B11" t="s">
         <v>45</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D11">
@@ -1789,14 +1828,14 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" ht="19.2" spans="1:9">
       <c r="A12" t="s">
         <v>48</v>
       </c>
       <c r="B12" t="s">
         <v>45</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D12">
@@ -1819,14 +1858,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" ht="19.2" spans="1:9">
       <c r="A13" t="s">
         <v>51</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D13">
@@ -1849,14 +1888,14 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" ht="19.2" spans="1:9">
       <c r="A14" t="s">
         <v>54</v>
       </c>
       <c r="B14" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D14">
@@ -1873,20 +1912,20 @@
         <v>70</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" ht="19.2" spans="1:9">
       <c r="A15" t="s">
         <v>57</v>
       </c>
       <c r="B15" t="s">
         <v>45</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D15">
@@ -1903,20 +1942,20 @@
         <v>70</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" ht="19.2" spans="1:9">
       <c r="A16" t="s">
         <v>60</v>
       </c>
       <c r="B16" t="s">
         <v>61</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D16">
@@ -1939,14 +1978,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" ht="19.2" spans="1:9">
       <c r="A17" t="s">
         <v>64</v>
       </c>
       <c r="B17" t="s">
         <v>61</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D17">
@@ -1969,14 +2008,14 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" ht="19.2" spans="1:9">
       <c r="A18" t="s">
         <v>67</v>
       </c>
       <c r="B18" t="s">
         <v>61</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="3" t="s">
         <v>68</v>
       </c>
       <c r="D18">
@@ -1993,20 +2032,20 @@
         <v>60</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" ht="19.2" spans="1:9">
       <c r="A19" t="s">
         <v>70</v>
       </c>
       <c r="B19" t="s">
         <v>61</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D19">
@@ -2023,20 +2062,20 @@
         <v>60</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" ht="19.2" spans="1:9">
       <c r="A20" t="s">
         <v>73</v>
       </c>
       <c r="B20" t="s">
         <v>61</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D20">
@@ -2053,20 +2092,20 @@
         <v>60</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" ht="19.2" spans="1:9">
       <c r="A21" t="s">
         <v>76</v>
       </c>
       <c r="B21" t="s">
         <v>77</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D21">
@@ -2083,20 +2122,20 @@
         <v>50</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" ht="19.2" spans="1:9">
       <c r="A22" t="s">
         <v>80</v>
       </c>
       <c r="B22" t="s">
         <v>77</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="3" t="s">
         <v>81</v>
       </c>
       <c r="D22">
@@ -2113,20 +2152,20 @@
         <v>50</v>
       </c>
       <c r="H22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" ht="19.2" spans="1:9">
       <c r="A23" t="s">
         <v>83</v>
       </c>
       <c r="B23" t="s">
         <v>77</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
         <v>84</v>
       </c>
       <c r="D23">
@@ -2143,20 +2182,20 @@
         <v>50</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" ht="19.2" spans="1:9">
       <c r="A24" t="s">
         <v>86</v>
       </c>
       <c r="B24" t="s">
         <v>77</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3" t="s">
         <v>87</v>
       </c>
       <c r="D24">
@@ -2173,20 +2212,20 @@
         <v>50</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I24" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" ht="19.2" spans="1:9">
       <c r="A25" t="s">
         <v>89</v>
       </c>
       <c r="B25" t="s">
         <v>77</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="3" t="s">
         <v>90</v>
       </c>
       <c r="D25">
@@ -2203,10 +2242,70 @@
         <v>50</v>
       </c>
       <c r="H25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" ht="19.2" spans="1:9">
+      <c r="A26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26">
+        <v>530000</v>
+      </c>
+      <c r="E26">
+        <f>ROUND(D26/1000,0)*2</f>
+        <v>1060</v>
+      </c>
+      <c r="F26">
         <v>25</v>
+      </c>
+      <c r="G26">
+        <v>50</v>
+      </c>
+      <c r="H26">
+        <v>7</v>
+      </c>
+      <c r="I26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" ht="19.2" spans="1:9">
+      <c r="A27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27">
+        <v>565000</v>
+      </c>
+      <c r="E27">
+        <f>ROUND(D27/1000,0)*2</f>
+        <v>1130</v>
+      </c>
+      <c r="F27">
+        <v>25</v>
+      </c>
+      <c r="G27">
+        <v>50</v>
+      </c>
+      <c r="H27">
+        <v>7</v>
+      </c>
+      <c r="I27" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/Planet.xlsx
+++ b/JsonConverter/ExcelFiles/Planet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9000"/>
+    <workbookView windowWidth="13272" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
     <t>BaseOre</t>
   </si>
   <si>
-    <t>Property</t>
+    <t>Properity</t>
   </si>
   <si>
     <t>Grade</t>
@@ -1632,7 +1632,7 @@
         <v>18000</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:E25" si="0">ROUND(D5/1000,0)*2</f>
+        <f t="shared" ref="E5:E27" si="0">ROUND(D5/1000,0)*2</f>
         <v>36</v>
       </c>
       <c r="F5">
@@ -2262,7 +2262,7 @@
         <v>530000</v>
       </c>
       <c r="E26">
-        <f>ROUND(D26/1000,0)*2</f>
+        <f t="shared" si="0"/>
         <v>1060</v>
       </c>
       <c r="F26">
@@ -2292,7 +2292,7 @@
         <v>565000</v>
       </c>
       <c r="E27">
-        <f>ROUND(D27/1000,0)*2</f>
+        <f t="shared" si="0"/>
         <v>1130</v>
       </c>
       <c r="F27">

--- a/JsonConverter/ExcelFiles/Planet.xlsx
+++ b/JsonConverter/ExcelFiles/Planet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13272" windowHeight="9000"/>
+    <workbookView windowWidth="16524" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1606,7 +1606,7 @@
         <v>26</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>80</v>
@@ -1636,7 +1636,7 @@
         <v>36</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>80</v>
@@ -1666,7 +1666,7 @@
         <v>50</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>80</v>
@@ -1696,7 +1696,7 @@
         <v>60</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>80</v>
@@ -1726,7 +1726,7 @@
         <v>76</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>80</v>
@@ -1756,7 +1756,7 @@
         <v>90</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>80</v>
@@ -1786,7 +1786,7 @@
         <v>98</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>80</v>
@@ -1816,7 +1816,7 @@
         <v>110</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>70</v>
@@ -1846,7 +1846,7 @@
         <v>156</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>70</v>
@@ -1876,7 +1876,7 @@
         <v>220</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>70</v>
@@ -1906,7 +1906,7 @@
         <v>270</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>70</v>
@@ -1936,7 +1936,7 @@
         <v>296</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>70</v>
@@ -1966,7 +1966,7 @@
         <v>330</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G16">
         <v>60</v>
@@ -1996,7 +1996,7 @@
         <v>390</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G17">
         <v>60</v>
@@ -2026,7 +2026,7 @@
         <v>480</v>
       </c>
       <c r="F18">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G18">
         <v>60</v>
@@ -2056,7 +2056,7 @@
         <v>550</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G19">
         <v>60</v>
@@ -2086,7 +2086,7 @@
         <v>596</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G20">
         <v>60</v>
@@ -2116,7 +2116,7 @@
         <v>640</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G21">
         <v>50</v>
@@ -2146,7 +2146,7 @@
         <v>730</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G22">
         <v>50</v>
@@ -2176,7 +2176,7 @@
         <v>820</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G23">
         <v>50</v>
@@ -2206,7 +2206,7 @@
         <v>920</v>
       </c>
       <c r="F24">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G24">
         <v>50</v>
@@ -2236,7 +2236,7 @@
         <v>990</v>
       </c>
       <c r="F25">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G25">
         <v>50</v>
@@ -2266,7 +2266,7 @@
         <v>1060</v>
       </c>
       <c r="F26">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G26">
         <v>50</v>
@@ -2296,7 +2296,7 @@
         <v>1130</v>
       </c>
       <c r="F27">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G27">
         <v>50</v>

--- a/JsonConverter/ExcelFiles/Planet.xlsx
+++ b/JsonConverter/ExcelFiles/Planet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16524" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1599,17 +1599,17 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="E4">
         <f>ROUND(D4/1000,0)*2</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1636,10 +1636,10 @@
         <v>36</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1666,10 +1666,10 @@
         <v>50</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1696,10 +1696,10 @@
         <v>60</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1726,10 +1726,10 @@
         <v>76</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -1756,10 +1756,10 @@
         <v>90</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -1786,10 +1786,10 @@
         <v>98</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -1816,10 +1816,10 @@
         <v>110</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G11">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -1846,10 +1846,10 @@
         <v>156</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G12">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -1876,10 +1876,10 @@
         <v>220</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G13">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -1906,10 +1906,10 @@
         <v>270</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G14">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H14">
         <v>3</v>
@@ -1936,10 +1936,10 @@
         <v>296</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G15">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H15">
         <v>3</v>
@@ -1966,10 +1966,10 @@
         <v>330</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G16">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H16">
         <v>3</v>
@@ -1996,10 +1996,10 @@
         <v>390</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G17">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H17">
         <v>3</v>
@@ -2026,10 +2026,10 @@
         <v>480</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G18">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H18">
         <v>4</v>
@@ -2056,10 +2056,10 @@
         <v>550</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G19">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H19">
         <v>4</v>
@@ -2086,10 +2086,10 @@
         <v>596</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G20">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H20">
         <v>4</v>
@@ -2116,7 +2116,7 @@
         <v>640</v>
       </c>
       <c r="F21">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G21">
         <v>50</v>
@@ -2146,7 +2146,7 @@
         <v>730</v>
       </c>
       <c r="F22">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G22">
         <v>50</v>
@@ -2176,7 +2176,7 @@
         <v>820</v>
       </c>
       <c r="F23">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G23">
         <v>50</v>
@@ -2206,7 +2206,7 @@
         <v>920</v>
       </c>
       <c r="F24">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G24">
         <v>50</v>
@@ -2236,7 +2236,7 @@
         <v>990</v>
       </c>
       <c r="F25">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G25">
         <v>50</v>
@@ -2266,7 +2266,7 @@
         <v>1060</v>
       </c>
       <c r="F26">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G26">
         <v>50</v>
@@ -2296,7 +2296,7 @@
         <v>1130</v>
       </c>
       <c r="F27">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G27">
         <v>50</v>

--- a/JsonConverter/ExcelFiles/Planet.xlsx
+++ b/JsonConverter/ExcelFiles/Planet.xlsx
@@ -87,7 +87,7 @@
     <t>BaseOre</t>
   </si>
   <si>
-    <t>Properity</t>
+    <t>Prosperity</t>
   </si>
   <si>
     <t>Grade</t>
